--- a/光伏配储项目/电价数据/2026/文山站.xlsx
+++ b/光伏配储项目/电价数据/2026/文山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5450499999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.04326</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6288400000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7087100000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.63326</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45263</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4684700000000001</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5183099999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.42509</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.14133</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.18021</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.14553</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.61287</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.65349</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.78971</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.43917</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.62337</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.7569199999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.49267</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5507799999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.7637</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.96576</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.82996</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.31881</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5221699999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.71101</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.09308</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.13426</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.78062</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8903799999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.25707</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.98126</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.96758</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8747999999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5897100000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47911</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42163</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.81187</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.47402</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90532</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.0868</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5363300000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.56924</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.8112</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7285199999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47249</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.53992</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.7997799999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.95977</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.70748</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.47365</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.72348</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.8794299999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.62634</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.14287</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.60887</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.04363</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8412500000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.6399199999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.09175</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.21327</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.55931</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54652</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.6650499999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.7043400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.47897</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.26086</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.27134</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18672</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.58726</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.62391</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.18418</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.11253</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6441699999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.56585</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.50197</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.24164</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.5518999999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7844800000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9384400000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33334</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5189900000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50561</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5603899999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.47236</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.70429</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.9382</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.76291</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5419299999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.53461</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.67013</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48472</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.87517</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.9472200000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7832899999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8824500000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.08149</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.6679400000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5555599999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6198899999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64183</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.66067</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50696</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.59666</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.6642400000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.64986</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.4141</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6942200000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.33153</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6841699999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.11243</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.14884</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.70926</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9163300000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.72027</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.96378</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.34856</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.50898</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.58487</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.79967</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.57304</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.05979</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.7141900000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.73505</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.72112</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.69421</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.77379</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.74618</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.5686599999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.52339</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.46692</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34316</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.64538</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.54953</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6662100000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.68486</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47434</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.51789</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.6328400000000001</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.80192</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.75613</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.87052</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.47351</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.11974</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.58986</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.77236</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.42546</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.78562</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.69675</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.57397</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.20115</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.56126</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.73912</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.01447</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.7220800000000001</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.48643</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.8948400000000001</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.8587899999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.6028300000000001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.9202400000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.48438</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.8570099999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.5658300000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.58211</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.6003200000000001</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.7889700000000001</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.94504</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.7999700000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.91016</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.63903</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.82897</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.8249099999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.95652</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.11187</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.19894</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.78501</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.6177999999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.60034</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.5855199999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.98294</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31658</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.65542</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.19185</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.5627799999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.6676</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.48174</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.26229</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.57112</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.25623</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.66516</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.5534600000000001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.46341</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.18417</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.02097</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34442</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.79647</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.53467</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5600599999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.45998</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.05052</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.23622</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.02773</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.23904</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.06608</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.22288</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.09451999999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.006160000000000001</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.23373</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.22439</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.23467</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.02768</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.01958</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.24898</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.22859</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.19193</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3307</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.41512</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.14077</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.20021</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.24258</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.16411</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.47654</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.54064</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.02625</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.48852</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.47213</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.51751</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.22907</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.23559</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.53535</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5609400000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.66079</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.55676</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.83099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.03755</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.57862</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.03858</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.55867</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.48268</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.75083</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.3322</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.0234</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.56192</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.43269</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.13001</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5865900000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79076</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77735</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87374</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49292</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20711</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53851</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50225</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46275</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45506</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40345</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5972499999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4352200000000001</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.54606</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65495</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.11505</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5087900000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.40537</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.6391</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8858400000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.29491</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.24803</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.30729</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.83008</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.52449</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.57256</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.4742</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.62071</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57772</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5102599999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.5102099999999999</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.67495</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.12963</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.18723</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45726</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35773</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9559</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47118</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48593</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.21757</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.43812</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.50186</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.80079</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.94116</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.48676</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.55325</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.42889</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.6342300000000001</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.13007</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.21008</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.62965</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.50673</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.52398</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.46365</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.43502</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.08450000000000001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.06451000000000001</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.26917</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.47266</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.13527</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.43878</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.64323</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.80261</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.8100599999999999</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.72865</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.23278</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.48865</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.22427</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.05414</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.5494</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.97142</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.28884</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.71669</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.23886</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.10766</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.03217</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.94197</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.65262</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.68537</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.37419</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.19536</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.66627</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.17921</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.5500900000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.7746799999999999</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.7606499999999999</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.68221</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.79257</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.74166</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.99574</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.70678</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.7261299999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.27683</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.57651</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.64255</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.71623</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.5483899999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.25378</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.5396299999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.60461</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.71827</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.50108</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.46257</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.61545</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.71976</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5754900000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.51797</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32499</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.22013</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.79755</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.68432</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6004700000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39123</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.49063</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26582</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.64371</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6499400000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8882599999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.3429</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.22934</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.89085</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.72642</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.98388</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.22827</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.17699</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.07681</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.55553</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.50278</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41877</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.52665</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.66931</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.85912</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.85072</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.83945</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.84045</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.6549</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.49366</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.99518</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.13857</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.69619</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.06566</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.68007</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.56101</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.55376</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.62099</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.86225</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.37596</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.8122</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.4381</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.01984</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.8323200000000001</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.5534</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.53648</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.57028</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.58367</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.5787</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.55556</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.58007</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.22467</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.61286</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.69496</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.75496</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.61042</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.61823</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.62643</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.55472</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.66074</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.07454</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.19209</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.60427</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.61276</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.60644</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.68621</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.63634</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.71317</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5945900000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.62998</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.64781</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.33434</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.46146</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9118200000000001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.65543</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.47078</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.8220599999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.37238</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.04975</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.94313</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.79525</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50703</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34927</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.65513</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.47421</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.39063</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.5996699999999999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517000000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8321000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3448</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44679</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.53013</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5751499999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7941900000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.8049299999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.24475</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25098</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.59462</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.51562</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.78472</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.8031</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51807</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.46358</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.07124</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.59365</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.52651</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.17448</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.18679</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.17132</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.03984</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.04554</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9410700000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.11579</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.06394</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.0648</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.94226</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.73362</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.10267</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.75842</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.2584</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.96475</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.8031200000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9944400000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7413500000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.0914</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.38598</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.0174</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.69974</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.76716</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.7333500000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42254</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45222</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56329</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50227</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5178400000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45568</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.40555</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.53692</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.00017</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.07632</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.36015</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.41254</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.30943</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.0544</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.85292</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.32187</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.43503</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.46595</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.82573</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.47155</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.52455</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.5442899999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5215299999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.47709</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.4407</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.03351</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.03472</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.06268</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.82863</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.8974800000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.55148</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.88282</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.33093</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.55175</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.12369</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.65921</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.54796</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.8523200000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.91604</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47771</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.66973</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.47134</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.83361</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.43669</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.60215</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.8121499999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.30938</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.60343</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.6399199999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.5554199999999999</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.69953</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.03948</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.52889</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.01435</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5396</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5893699999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22513</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.46636</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36412</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.68987</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.96369</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5309199999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43543</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.4352200000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35242</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.66283</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21598</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.16922</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.25856</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.24146</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.23373</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.23376</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.13123</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.06465</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.22932</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.25423</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.23781</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.22806</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.5290499999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.22604</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.23683</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.22785</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.23838</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.70921</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.43188</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.39394</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.9497100000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.08396</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.52537</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.56147</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.45938</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.64135</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.6241100000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.47718</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.69757</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.64615</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.03395</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.0375</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.81516</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.65828</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.46931</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.8001200000000001</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.23211</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.46731</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.47427</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.24141</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.57053</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5714600000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.59704</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.70005</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.7671699999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.45087</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.48997</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.5092099999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.8001699999999999</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.45509</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.50973</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.52066</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.03277</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.04094</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.38496</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.68103</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.03326</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.19574</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.37328</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8768400000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.60689</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.00736</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.89513</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.6634099999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34094</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5139199999999999</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.70901</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.50481</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.66291</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6642100000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.51051</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.50797</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.79645</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.80277</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.91013</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.82321</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.9126599999999999</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.37475</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.3696</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.85253</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5725800000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.57973</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.18571</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.49485</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.56813</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.45833</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.5852200000000001</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.33815</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.9182</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.52595</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.45304</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.45777</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.46363</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.52144</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.51085</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.47216</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.46221</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.50812</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.5871799999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.80777</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.70123</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.59745</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.9337000000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7505499999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.59116</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.7936299999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.42021</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.46154</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49439</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.46824</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.43524</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54687</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.8338</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.78388</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.5800599999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.65127</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.51049</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.52937</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.16065</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.37183</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.43911</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.50891</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.51903</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.87395</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.60049</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.85582</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.25507</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.52003</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.44304</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.31533</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.33771</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.38693</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.45455</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.4372</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.50618</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.51862</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.49719</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.9884299999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.86594</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.69841</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8016</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.14257</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.13148</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.8011</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.90296</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.69594</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.56099</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5617300000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.6672400000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6941499999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45855</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36872</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.54173</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.46435</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.48157</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.42102</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.5448500000000001</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.6066900000000001</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.6143200000000001</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.59721</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.5974299999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.63417</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.64877</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.57877</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.25744</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.15985</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.44799</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.0768</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.34783</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.35439</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.46289</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.37494</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.4667</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.44847</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.48061</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.48027</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.40086</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.92616</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.9112899999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.50564</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.58281</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.9088200000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.8882899999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.52921</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6993200000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.82989</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.5270900000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.87078</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.85056</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.18542</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.12374</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.8915700000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.7299600000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.5578200000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.71097</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37514</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.66675</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8493099999999999</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.38701</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.05471</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.98502</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.01115</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.00922</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.15443</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.94286</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.91499</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.72149</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.99434</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.14091</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.13443</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.2332</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.93509</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.75444</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.18509</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.60295</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.18433</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.18389</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.17392</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.18284</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5474600000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.27656</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.47931</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.16562</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.2554</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.7032200000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.10561</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.68069</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.55477</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.01428</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.12008</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.19168</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.10155</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.11216</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.21102</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.18278</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21841</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.23652</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.7995800000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.20588</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.80013</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.17101</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.15179</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.17962</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.23105</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.2515</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.23182</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.56608</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.32221</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.38192</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.37384</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.68612</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.11841</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.53095</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.86195</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.46102</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.73289</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.73819</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.75898</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.95413</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.02088</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.08845</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.09156</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.53122</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.21735</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.05047</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.87775</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.3351</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.72193</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.54905</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.86568</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.64137</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.79172</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.74807</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5975499999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.52037</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.50313</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.38763</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.99391</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.32259</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.97787</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.05031</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.03056</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.77785</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.75867</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.22884</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.79695</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.88812</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.7115900000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.23077</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.41261</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.77275</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8178200000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56955</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.96462</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8633099999999999</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.86372</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.56662</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.56028</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5602999999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5200900000000001</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.56033</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52661</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.44123</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.55969</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5331</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5325800000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.57213</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.20573</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.90416</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.53708</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.76558</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.74685</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.55358</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56971</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.85082</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.80067</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.60192</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.88201</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.2211</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.7200700000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.57435</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.98481</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.56814</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.57367</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.8210700000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.57831</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.8375499999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.87162</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.20738</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.81908</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.69977</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.5801900000000001</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.19402</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.14041</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.10554</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.10436</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.86429</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.70001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5628</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.5635399999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7037899999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8471599999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.52765</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.68833</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.64525</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.04319</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.52938</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6183099999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.53006</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5761799999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.55908</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.61461</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.71313</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6137100000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5347499999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51624</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38404</v>
       </c>
     </row>
   </sheetData>
